--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487108_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487108_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1807</v>
+        <v>4.6011</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5495</v>
+        <v>3.8093</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6311</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>3.2839</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7244</v>
+        <v>-0.3041</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3437</v>
+        <v>-0.0839</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3808</v>
+        <v>-0.2201</v>
       </c>
       <c r="V2" t="n">
         <v>0.6562</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. URTXULUTEGI NAVARRI</t>
+          <t>A. ARMENDARIZ LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2133</v>
+        <v>3.8525</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9429</v>
+        <v>3.2482</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7296</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5131</v>
+        <v>2.0893</v>
       </c>
       <c r="H3" t="n">
-        <v>1.782</v>
+        <v>1.5845</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7311</v>
+        <v>0.5048</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5872</v>
+        <v>3.8037</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1627</v>
+        <v>2.4527</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4245</v>
+        <v>1.3509</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0741</v>
+        <v>-1.7144</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3808</v>
+        <v>-0.8682</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6933</v>
+        <v>-0.8461</v>
       </c>
       <c r="P3" t="n">
-        <v>0.579</v>
+        <v>0.772</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.965</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3914</v>
+        <v>0.9911</v>
       </c>
       <c r="T3" t="n">
-        <v>1.363</v>
+        <v>0.4095</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0284</v>
+        <v>0.5816</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2702</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0422</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ARMENDARIZ LOPEZ</t>
+          <t>J. URTXULUTEGI NAVARRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9592</v>
+        <v>2.4637</v>
       </c>
       <c r="E4" t="n">
-        <v>2.569</v>
+        <v>3.2201</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3902</v>
+        <v>-0.7564</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0893</v>
+        <v>2.5131</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5845</v>
+        <v>1.782</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5048</v>
+        <v>0.7311</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8037</v>
+        <v>3.5872</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4527</v>
+        <v>2.1627</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3509</v>
+        <v>1.4245</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7144</v>
+        <v>-1.0741</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8682</v>
+        <v>-0.3808</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8461</v>
+        <v>-0.6933</v>
       </c>
       <c r="P4" t="n">
-        <v>0.772</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0978</v>
+        <v>0.6418</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2697</v>
+        <v>0.6402</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3675</v>
+        <v>0.0016</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.2702</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.0422</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. ETXEBERRIA AGUIRREZABALA</t>
+          <t>E. HUIZI ZUBELDIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9189</v>
+        <v>1.7183</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4504</v>
+        <v>1.2899</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5315</v>
+        <v>0.4284</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8474</v>
+        <v>1.7901</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5518</v>
+        <v>0.1635</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7044</v>
+        <v>1.6265</v>
       </c>
       <c r="J5" t="n">
-        <v>4.395</v>
+        <v>2.8974</v>
       </c>
       <c r="K5" t="n">
-        <v>4.8591</v>
+        <v>1.5058</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4641</v>
+        <v>1.3916</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5476</v>
+        <v>-1.1074</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3073</v>
+        <v>-1.3423</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2403</v>
+        <v>0.2349</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0715</v>
+        <v>-0.2142</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9928</v>
+        <v>-0.2915</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0787</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.842</v>
+        <v>-0.2436</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0422</v>
+        <v>0.614</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.7997</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GORDILLO BELTRAN</t>
+          <t>A. IRASTORZA EZKIAGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8386</v>
+        <v>1.2312</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4096</v>
+        <v>1.5096</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.571</v>
+        <v>-0.2784</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3979</v>
+        <v>-1.208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5382</v>
+        <v>-0.9688</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9361</v>
+        <v>-0.2392</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1368</v>
+        <v>-0.2336</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1125</v>
+        <v>-0.2743</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0243</v>
+        <v>0.0407</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5347</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5743</v>
+        <v>-0.6944</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9604</v>
+        <v>-0.2799</v>
       </c>
       <c r="P6" t="n">
         <v>0.579</v>
@@ -922,28 +922,28 @@
         <v>0.579</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9856</v>
+        <v>0.3041</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6009</v>
+        <v>0.2294</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3847</v>
+        <v>0.0747</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3281</v>
+        <v>1.5561</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3281</v>
+        <v>1.5138</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. IRASTORZA EZKIAGA</t>
+          <t>A. GORDILLO BELTRAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3779</v>
+        <v>0.9959</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7099</v>
+        <v>1.7275</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3319</v>
+        <v>-0.7316</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.208</v>
+        <v>-0.3979</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9688</v>
+        <v>0.5382</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2392</v>
+        <v>-0.9361</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2336</v>
+        <v>1.1368</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2743</v>
+        <v>1.1125</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>0.0243</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-1.5347</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6944</v>
+        <v>-0.5743</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2799</v>
+        <v>-0.9604</v>
       </c>
       <c r="P7" t="n">
         <v>0.579</v>
@@ -1000,28 +1000,28 @@
         <v>0.579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4508</v>
+        <v>1.1429</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4297</v>
+        <v>0.9188</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0211</v>
+        <v>0.2241</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5561</v>
+        <v>-0.3281</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5138</v>
+        <v>-0.3281</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. HUIZI ZUBELDIA</t>
+          <t>B. ETXEBERRIA AGUIRREZABALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3138</v>
+        <v>0.7688</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5106000000000001</v>
+        <v>2.0499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8032</v>
+        <v>-1.2811</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7901</v>
+        <v>2.8474</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1635</v>
+        <v>4.5518</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6265</v>
+        <v>-1.7044</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8974</v>
+        <v>4.395</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5058</v>
+        <v>4.8591</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3916</v>
+        <v>-0.4641</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1074</v>
+        <v>-1.5476</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3423</v>
+        <v>-0.3073</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2349</v>
+        <v>-1.2403</v>
       </c>
       <c r="P8" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6187</v>
+        <v>0.9214</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0708</v>
+        <v>0.5923</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4521</v>
+        <v>0.3291</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2436</v>
+        <v>-1.842</v>
       </c>
       <c r="W8" t="n">
-        <v>0.614</v>
+        <v>-0.0422</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.8576</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ELOSEGUI OLANO</t>
+          <t>U. CONDE LAKUNTZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5049</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2594</v>
+        <v>-0.3386</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2456</v>
+        <v>0.2485</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5433</v>
+        <v>-0.1041</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.177</v>
+        <v>-0.3726</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3663</v>
+        <v>0.2685</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7245</v>
+        <v>0.4088</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6269</v>
+        <v>0.5612</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6408</v>
+        <v>-1.0741</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9014</v>
+        <v>-0.7813</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2606</v>
+        <v>-0.2928</v>
       </c>
       <c r="P9" t="n">
-        <v>0.386</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>0.386</v>
+        <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3477</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3569</v>
+        <v>0.3586</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0092</v>
+        <v>0.3576</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. CONDE LAKUNTZA</t>
+          <t>J. ELOSEGUI OLANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3443</v>
+        <v>-0.0905</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.218</v>
+        <v>-0.0591</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1263</v>
+        <v>-0.0314</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1041</v>
+        <v>-0.5433</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3726</v>
+        <v>-0.177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2685</v>
+        <v>-0.3663</v>
       </c>
       <c r="J10" t="n">
-        <v>0.97</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4088</v>
+        <v>0.7245</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5612</v>
+        <v>-0.6269</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0741</v>
+        <v>-0.6408</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7813</v>
+        <v>-0.9014</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2928</v>
+        <v>0.2606</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8951</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.538</v>
+        <v>0.0668</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5208</v>
+        <v>-0.1566</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0172</v>
+        <v>0.2234</v>
       </c>
       <c r="V10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2596</v>
+        <v>-3.1456</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5686</v>
+        <v>-1.6688</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6909</v>
+        <v>-1.4768</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7784</v>
@@ -1312,13 +1312,13 @@
         <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8672</v>
+        <v>-0.7532</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0727</v>
+        <v>-0.0274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9399</v>
+        <v>-0.7258</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8401</v>
+        <v>-3.5595</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3822</v>
+        <v>-2.1819</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4579</v>
+        <v>-1.3776</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2824</v>
@@ -1390,13 +1390,13 @@
         <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2915</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0132</v>
+        <v>0.2135</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2783</v>
+        <v>0.3586</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2702</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.8535</v>
+        <v>8.745899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7137</v>
+        <v>12.6061</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8602</v>
+        <v>-3.860300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>5.209700000000001</v>
@@ -1441,7 +1441,7 @@
         <v>1.970600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>20.45519999999999</v>
+        <v>20.4552</v>
       </c>
       <c r="K13" t="n">
         <v>12.8222</v>
@@ -1453,7 +1453,7 @@
         <v>-15.2454</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.582799999999999</v>
+        <v>-9.582800000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-5.6624</v>
@@ -1468,10 +1468,10 @@
         <v>14.4757</v>
       </c>
       <c r="S13" t="n">
-        <v>3.192599999999999</v>
+        <v>4.0849</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9104</v>
+        <v>2.8029</v>
       </c>
       <c r="U13" t="n">
         <v>1.2821</v>
@@ -1483,7 +1483,7 @@
         <v>2.8588</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.3726</v>
+        <v>-4.372599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6244</v>
+        <v>2.6581</v>
       </c>
       <c r="E14" t="n">
-        <v>3.7317</v>
+        <v>3.6316</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1073</v>
+        <v>-0.9734</v>
       </c>
       <c r="G14" t="n">
         <v>3.515</v>
@@ -1546,13 +1546,13 @@
         <v>1.5441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9208</v>
+        <v>-0.887</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2842</v>
+        <v>-0.3843</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.5027</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5138</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.372</v>
+        <v>1.6863</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4659</v>
+        <v>1.566</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.1203</v>
       </c>
       <c r="G15" t="n">
         <v>2.5221</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1851</v>
+        <v>0.1292</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1361</v>
+        <v>-0.036</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0489</v>
+        <v>0.1652</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.821</v>
+        <v>1.1131</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8592</v>
+        <v>1.6603</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0382</v>
+        <v>-0.5472</v>
       </c>
       <c r="G16" t="n">
         <v>-0.0862</v>
@@ -1702,13 +1702,13 @@
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0397</v>
+        <v>0.2525</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1012</v>
+        <v>-0.3001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0615</v>
+        <v>0.5525</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2112</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MENDIVIL ODERIZ</t>
+          <t>P. OSES TOME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0044</v>
+        <v>0.1168</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4599</v>
+        <v>3.4641</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4555</v>
+        <v>-3.3473</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.4103</v>
+        <v>1.6133</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3361</v>
+        <v>-0.0682</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0742</v>
+        <v>1.6815</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5739</v>
+        <v>4.5433</v>
       </c>
       <c r="K17" t="n">
-        <v>1.128</v>
+        <v>1.3609</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5541</v>
+        <v>3.1824</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9843</v>
+        <v>-2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.4641</v>
+        <v>-1.4292</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5202</v>
+        <v>-1.5009</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0094</v>
+        <v>-0.9247</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6882</v>
+        <v>-0.3771</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3212</v>
+        <v>-0.5476</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5983</v>
+        <v>-0.5717</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1278</v>
+        <v>1.228</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5295</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5628</v>
+        <v>-0.2555</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8949</v>
+        <v>-0.6947</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3321</v>
+        <v>0.4392</v>
       </c>
       <c r="G18" t="n">
         <v>0.6574</v>
@@ -1858,13 +1858,13 @@
         <v>0.579</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.5268</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7139</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1203</v>
+        <v>-0.0132</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. OSES TOME</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6512</v>
+        <v>-0.4581</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9634</v>
+        <v>-0.0157</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.6147</v>
+        <v>-0.4424</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6133</v>
+        <v>-1.547</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0682</v>
+        <v>-0.5816</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6815</v>
+        <v>-0.9654</v>
       </c>
       <c r="J19" t="n">
-        <v>4.5433</v>
+        <v>-0.1522</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3609</v>
+        <v>-0.2743</v>
       </c>
       <c r="L19" t="n">
-        <v>3.1824</v>
+        <v>0.1221</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.93</v>
+        <v>-1.3948</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4292</v>
+        <v>-0.3073</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5009</v>
+        <v>-1.0875</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0.579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9301</v>
+        <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6928</v>
+        <v>0.1818</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8778</v>
+        <v>0.1365</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8149999999999999</v>
+        <v>0.0453</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5717</v>
+        <v>0.3281</v>
       </c>
       <c r="W19" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7997</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8872</v>
+        <v>-0.8138</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0395</v>
+        <v>-0.9394</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1523</v>
+        <v>0.1256</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1438</v>
@@ -2014,13 +2014,13 @@
         <v>0.386</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4924</v>
+        <v>-0.4191</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.238</v>
+        <v>-0.1378</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2545</v>
+        <v>-0.2813</v>
       </c>
       <c r="V20" t="n">
         <v>0.3281</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>J. MENDIVIL ODERIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0794</v>
+        <v>-1.5116</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3161</v>
+        <v>1.1581</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7633</v>
+        <v>-2.6697</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.547</v>
+        <v>-3.4103</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5816</v>
+        <v>-1.3361</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9654</v>
+        <v>-2.0742</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1522</v>
+        <v>0.5739</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2743</v>
+        <v>1.128</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>-0.5541</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3948</v>
+        <v>-3.9843</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3073</v>
+        <v>-2.4641</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0875</v>
+        <v>-1.5202</v>
       </c>
       <c r="P21" t="n">
-        <v>0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4396</v>
+        <v>0.4934</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1639</v>
+        <v>0.3864</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2756</v>
+        <v>0.107</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3281</v>
+        <v>1.5983</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.1278</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3281</v>
+        <v>-0.5295</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4836</v>
+        <v>-1.8643</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3421</v>
+        <v>-0.6425</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1414</v>
+        <v>-1.2217</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8755</v>
@@ -2170,13 +2170,13 @@
         <v>0.386</v>
       </c>
       <c r="S22" t="n">
-        <v>0.971</v>
+        <v>0.5903</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5632</v>
+        <v>0.2628</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4078</v>
+        <v>0.3275</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ARIZTIMUÑO MORRAS</t>
+          <t>M. BIDAURRE SOLA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9802</v>
+        <v>-3.6436</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3003</v>
+        <v>-2.5266</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6799</v>
+        <v>-1.1171</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1151</v>
+        <v>-3.3396</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4254</v>
+        <v>-1.6559</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6897</v>
+        <v>-1.6836</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.185</v>
+        <v>-2.1914</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0038</v>
+        <v>-0.9212</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1888</v>
+        <v>-1.2702</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.93</v>
+        <v>-1.1481</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4292</v>
+        <v>-0.7347</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5009</v>
+        <v>-0.4134</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7371</v>
+        <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2981</v>
+        <v>-0.8831</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5169</v>
+        <v>-0.3351</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8149999999999999</v>
+        <v>-0.548</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5561</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. BIDAURRE SOLA</t>
+          <t>M. ARIZTIMUÑO MORRAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.031</v>
+        <v>-4.2135</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7268</v>
+        <v>-2.801</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3041</v>
+        <v>-1.4125</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3396</v>
+        <v>-3.1151</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6559</v>
+        <v>-0.4254</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6836</v>
+        <v>-2.6897</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1914</v>
+        <v>-0.185</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9212</v>
+        <v>1.0038</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2702</v>
+        <v>-1.1888</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1481</v>
+        <v>-2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7347</v>
+        <v>-1.4292</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4134</v>
+        <v>-1.5009</v>
       </c>
       <c r="P24" t="n">
-        <v>0.579</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R24" t="n">
-        <v>0.579</v>
+        <v>1.7371</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2704</v>
+        <v>-0.5314</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5354</v>
+        <v>0.0162</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.735</v>
+        <v>-0.5476</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.5561</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.853599999999999</v>
+        <v>-7.1861</v>
       </c>
       <c r="E25" t="n">
-        <v>3.860399999999999</v>
+        <v>3.860200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-11.7138</v>
+        <v>-11.0462</v>
       </c>
       <c r="G25" t="n">
         <v>-5.209699999999999</v>
@@ -2380,10 +2380,10 @@
         <v>15.2454</v>
       </c>
       <c r="K25" t="n">
-        <v>9.583099999999998</v>
+        <v>9.5831</v>
       </c>
       <c r="L25" t="n">
-        <v>5.662399999999999</v>
+        <v>5.6624</v>
       </c>
       <c r="M25" t="n">
         <v>-20.4551</v>
@@ -2404,13 +2404,13 @@
         <v>13.5106</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.1927</v>
+        <v>-2.5249</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2822</v>
+        <v>-1.2821</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9104</v>
+        <v>-1.2429</v>
       </c>
       <c r="V25" t="n">
         <v>1.5139</v>
